--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -180,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -372,11 +372,154 @@
         <color rgb="00C9C2B3"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C2B3"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C2B3"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C2B3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C2B3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8862B"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -529,6 +672,16 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -861,6 +1014,19 @@
           <t>ALDER CREEK TRANSIT DISTRICT — OPERATIONS</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+      <c r="I1" s="54" t="n"/>
+      <c r="J1" s="54" t="n"/>
+      <c r="K1" s="54" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+      <c r="N1" s="54" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -881,18 +1047,18 @@
           <t>RunSchedule_Owl512.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
-      <c r="I4" s="24" t="n"/>
-      <c r="J4" s="24" t="n"/>
-      <c r="K4" s="24" t="n"/>
-      <c r="L4" s="24" t="n"/>
-      <c r="M4" s="24" t="n"/>
-      <c r="N4" s="24" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
+      <c r="J4" s="55" t="n"/>
+      <c r="K4" s="55" t="n"/>
+      <c r="L4" s="55" t="n"/>
+      <c r="M4" s="55" t="n"/>
+      <c r="N4" s="56" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="23" t="inlineStr">
@@ -905,18 +1071,18 @@
           <t>ACTD Scheduling &amp; Runcutting, Operations Division</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
-      <c r="I5" s="24" t="n"/>
-      <c r="J5" s="24" t="n"/>
-      <c r="K5" s="24" t="n"/>
-      <c r="L5" s="24" t="n"/>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="24" t="n"/>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="n"/>
+      <c r="L5" s="55" t="n"/>
+      <c r="M5" s="55" t="n"/>
+      <c r="N5" s="56" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -929,18 +1095,18 @@
           <t>Friday 10/17/2025 (owl block operating into Saturday 10/18/2025)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="55" t="n"/>
+      <c r="E6" s="55" t="n"/>
+      <c r="F6" s="55" t="n"/>
+      <c r="G6" s="55" t="n"/>
+      <c r="H6" s="55" t="n"/>
+      <c r="I6" s="55" t="n"/>
+      <c r="J6" s="55" t="n"/>
+      <c r="K6" s="55" t="n"/>
+      <c r="L6" s="55" t="n"/>
+      <c r="M6" s="55" t="n"/>
+      <c r="N6" s="56" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -953,18 +1119,18 @@
           <t>Fall 2025 Sign — Rev. 2 (effective 09/07/2025)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="55" t="n"/>
+      <c r="H7" s="55" t="n"/>
+      <c r="I7" s="55" t="n"/>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="55" t="n"/>
+      <c r="L7" s="55" t="n"/>
+      <c r="M7" s="55" t="n"/>
+      <c r="N7" s="56" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -977,18 +1143,18 @@
           <t>Official schedule of record</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="55" t="n"/>
+      <c r="H8" s="55" t="n"/>
+      <c r="I8" s="55" t="n"/>
+      <c r="J8" s="55" t="n"/>
+      <c r="K8" s="55" t="n"/>
+      <c r="L8" s="55" t="n"/>
+      <c r="M8" s="55" t="n"/>
+      <c r="N8" s="56" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
@@ -996,6 +1162,19 @@
           <t>Block Assignment Header</t>
         </is>
       </c>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="54" t="n"/>
+      <c r="L10" s="54" t="n"/>
+      <c r="M10" s="54" t="n"/>
+      <c r="N10" s="54" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -1008,9 +1187,9 @@
           <t>512-OWL</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
       <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Route:</t>
@@ -1021,13 +1200,13 @@
           <t>512 (Rivergate Downtown — South Main / Fifth Corridor Owl)</t>
         </is>
       </c>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
+      <c r="H11" s="55" t="n"/>
+      <c r="I11" s="55" t="n"/>
+      <c r="J11" s="55" t="n"/>
+      <c r="K11" s="55" t="n"/>
+      <c r="L11" s="55" t="n"/>
+      <c r="M11" s="55" t="n"/>
+      <c r="N11" s="56" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -1040,9 +1219,9 @@
           <t>4417</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
       <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Operator Name:</t>
@@ -1053,13 +1232,13 @@
           <t>Keeler, Raymond T.</t>
         </is>
       </c>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
+      <c r="H12" s="55" t="n"/>
+      <c r="I12" s="55" t="n"/>
+      <c r="J12" s="55" t="n"/>
+      <c r="K12" s="55" t="n"/>
+      <c r="L12" s="55" t="n"/>
+      <c r="M12" s="55" t="n"/>
+      <c r="N12" s="56" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
@@ -1072,9 +1251,9 @@
           <t>4177</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
       <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Assigned Division:</t>
@@ -1085,13 +1264,13 @@
           <t>Rivergate Yard (Div. 3)</t>
         </is>
       </c>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="24" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="24" t="n"/>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="24" t="n"/>
+      <c r="H13" s="55" t="n"/>
+      <c r="I13" s="55" t="n"/>
+      <c r="J13" s="55" t="n"/>
+      <c r="K13" s="55" t="n"/>
+      <c r="L13" s="55" t="n"/>
+      <c r="M13" s="55" t="n"/>
+      <c r="N13" s="56" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -1104,9 +1283,9 @@
           <t>10/17/2025 22:15</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
       <c r="F14" s="27" t="inlineStr">
         <is>
           <t>Scheduled Pullin:</t>
@@ -1117,13 +1296,13 @@
           <t>10/18/2025 05:30</t>
         </is>
       </c>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
+      <c r="H14" s="55" t="n"/>
+      <c r="I14" s="55" t="n"/>
+      <c r="J14" s="55" t="n"/>
+      <c r="K14" s="55" t="n"/>
+      <c r="L14" s="55" t="n"/>
+      <c r="M14" s="55" t="n"/>
+      <c r="N14" s="56" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -1136,9 +1315,9 @@
           <t>Fall 2025 Sign</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
       <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Bid Basis:</t>
@@ -1149,13 +1328,13 @@
           <t>Regular weekday owl (Fri→Sat)</t>
         </is>
       </c>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="24" t="n"/>
+      <c r="H15" s="55" t="n"/>
+      <c r="I15" s="55" t="n"/>
+      <c r="J15" s="55" t="n"/>
+      <c r="K15" s="55" t="n"/>
+      <c r="L15" s="55" t="n"/>
+      <c r="M15" s="55" t="n"/>
+      <c r="N15" s="56" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -1163,6 +1342,19 @@
           <t>Block Manifest — Trip Roster</t>
         </is>
       </c>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="54" t="n"/>
+      <c r="L17" s="54" t="n"/>
+      <c r="M17" s="54" t="n"/>
+      <c r="N17" s="54" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -2014,7 +2206,7 @@
       </c>
       <c r="L29" s="30" t="inlineStr">
         <is>
-          <t>04:57 (recovery)</t>
+          <t>04:46</t>
         </is>
       </c>
       <c r="M29" s="30" t="inlineStr">
@@ -2106,6 +2298,19 @@
           <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
         </is>
       </c>
+      <c r="B32" s="54" t="n"/>
+      <c r="C32" s="54" t="n"/>
+      <c r="D32" s="54" t="n"/>
+      <c r="E32" s="54" t="n"/>
+      <c r="F32" s="54" t="n"/>
+      <c r="G32" s="54" t="n"/>
+      <c r="H32" s="54" t="n"/>
+      <c r="I32" s="54" t="n"/>
+      <c r="J32" s="54" t="n"/>
+      <c r="K32" s="54" t="n"/>
+      <c r="L32" s="54" t="n"/>
+      <c r="M32" s="54" t="n"/>
+      <c r="N32" s="54" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
@@ -2157,19 +2362,19 @@
           <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
         </is>
       </c>
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="38" t="n"/>
-      <c r="E35" s="38" t="n"/>
-      <c r="F35" s="38" t="n"/>
-      <c r="G35" s="38" t="n"/>
-      <c r="H35" s="38" t="n"/>
-      <c r="I35" s="38" t="n"/>
-      <c r="J35" s="38" t="n"/>
-      <c r="K35" s="38" t="n"/>
-      <c r="L35" s="38" t="n"/>
-      <c r="M35" s="38" t="n"/>
-      <c r="N35" s="38" t="n"/>
+      <c r="B35" s="55" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
+      <c r="E35" s="55" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="55" t="n"/>
+      <c r="H35" s="55" t="n"/>
+      <c r="I35" s="55" t="n"/>
+      <c r="J35" s="55" t="n"/>
+      <c r="K35" s="55" t="n"/>
+      <c r="L35" s="55" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="56" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
@@ -2177,6 +2382,19 @@
           <t>Assignment Sign-Off</t>
         </is>
       </c>
+      <c r="B37" s="54" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="54" t="n"/>
+      <c r="F37" s="54" t="n"/>
+      <c r="G37" s="54" t="n"/>
+      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="54" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="54" t="n"/>
+      <c r="L37" s="54" t="n"/>
+      <c r="M37" s="54" t="n"/>
+      <c r="N37" s="54" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
@@ -2184,23 +2402,23 @@
           <t>Field</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="14" t="n"/>
+      <c r="C38" s="58" t="n"/>
+      <c r="D38" s="58" t="n"/>
+      <c r="E38" s="58" t="n"/>
+      <c r="F38" s="58" t="n"/>
+      <c r="G38" s="58" t="n"/>
+      <c r="H38" s="58" t="n"/>
+      <c r="I38" s="58" t="n"/>
+      <c r="J38" s="58" t="n"/>
+      <c r="K38" s="58" t="n"/>
+      <c r="L38" s="58" t="n"/>
+      <c r="M38" s="58" t="n"/>
+      <c r="N38" s="59" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
@@ -2213,18 +2431,18 @@
           <t>4417 / Keeler, Raymond T.</t>
         </is>
       </c>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="n"/>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="55" t="n"/>
+      <c r="F39" s="55" t="n"/>
+      <c r="G39" s="55" t="n"/>
+      <c r="H39" s="55" t="n"/>
+      <c r="I39" s="55" t="n"/>
+      <c r="J39" s="55" t="n"/>
+      <c r="K39" s="55" t="n"/>
+      <c r="L39" s="55" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="56" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
@@ -2237,18 +2455,18 @@
           <t>J. Amaya, Sched. Analyst II</t>
         </is>
       </c>
-      <c r="C40" s="39" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="39" t="n"/>
-      <c r="F40" s="39" t="n"/>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="39" t="n"/>
-      <c r="I40" s="39" t="n"/>
-      <c r="J40" s="39" t="n"/>
-      <c r="K40" s="39" t="n"/>
-      <c r="L40" s="39" t="n"/>
-      <c r="M40" s="39" t="n"/>
-      <c r="N40" s="39" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="55" t="n"/>
+      <c r="F40" s="55" t="n"/>
+      <c r="G40" s="55" t="n"/>
+      <c r="H40" s="55" t="n"/>
+      <c r="I40" s="55" t="n"/>
+      <c r="J40" s="55" t="n"/>
+      <c r="K40" s="55" t="n"/>
+      <c r="L40" s="55" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="56" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -2261,18 +2479,18 @@
           <t>R. Delcourt, Manager of Scheduling</t>
         </is>
       </c>
-      <c r="C41" s="24" t="n"/>
-      <c r="D41" s="24" t="n"/>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
-      <c r="I41" s="24" t="n"/>
-      <c r="J41" s="24" t="n"/>
-      <c r="K41" s="24" t="n"/>
-      <c r="L41" s="24" t="n"/>
-      <c r="M41" s="24" t="n"/>
-      <c r="N41" s="24" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="55" t="n"/>
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="55" t="n"/>
+      <c r="H41" s="55" t="n"/>
+      <c r="I41" s="55" t="n"/>
+      <c r="J41" s="55" t="n"/>
+      <c r="K41" s="55" t="n"/>
+      <c r="L41" s="55" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="56" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -2285,18 +2503,18 @@
           <t>09/02/2025</t>
         </is>
       </c>
-      <c r="C42" s="39" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="39" t="n"/>
-      <c r="F42" s="39" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="39" t="n"/>
-      <c r="I42" s="39" t="n"/>
-      <c r="J42" s="39" t="n"/>
-      <c r="K42" s="39" t="n"/>
-      <c r="L42" s="39" t="n"/>
-      <c r="M42" s="39" t="n"/>
-      <c r="N42" s="39" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="55" t="n"/>
+      <c r="H42" s="55" t="n"/>
+      <c r="I42" s="55" t="n"/>
+      <c r="J42" s="55" t="n"/>
+      <c r="K42" s="55" t="n"/>
+      <c r="L42" s="55" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="56" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
@@ -2309,18 +2527,18 @@
           <t>Rivergate Yard (Div. 3) — Owl Board</t>
         </is>
       </c>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="24" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="24" t="n"/>
-      <c r="H43" s="24" t="n"/>
-      <c r="I43" s="24" t="n"/>
-      <c r="J43" s="24" t="n"/>
-      <c r="K43" s="24" t="n"/>
-      <c r="L43" s="24" t="n"/>
-      <c r="M43" s="24" t="n"/>
-      <c r="N43" s="24" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="55" t="n"/>
+      <c r="F43" s="55" t="n"/>
+      <c r="G43" s="55" t="n"/>
+      <c r="H43" s="55" t="n"/>
+      <c r="I43" s="55" t="n"/>
+      <c r="J43" s="55" t="n"/>
+      <c r="K43" s="55" t="n"/>
+      <c r="L43" s="55" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="56" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -2333,18 +2551,18 @@
           <t>Fall 2025 Sign — Owl Sr. Board Line 12</t>
         </is>
       </c>
-      <c r="C44" s="39" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="39" t="n"/>
-      <c r="F44" s="39" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="39" t="n"/>
-      <c r="J44" s="39" t="n"/>
-      <c r="K44" s="39" t="n"/>
-      <c r="L44" s="39" t="n"/>
-      <c r="M44" s="39" t="n"/>
-      <c r="N44" s="39" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
+      <c r="E44" s="55" t="n"/>
+      <c r="F44" s="55" t="n"/>
+      <c r="G44" s="55" t="n"/>
+      <c r="H44" s="55" t="n"/>
+      <c r="I44" s="55" t="n"/>
+      <c r="J44" s="55" t="n"/>
+      <c r="K44" s="55" t="n"/>
+      <c r="L44" s="55" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -2405,6 +2623,11 @@
           <t>ALDER CREEK TRANSIT DISTRICT — AUTHORIZED OWL ROUTES</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -2420,11 +2643,11 @@
           <t>Purpose: Master list of Owl service routes authorized for operation during the Owl service window under the Fall 2025 Sign.</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n"/>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
+      <c r="B4" s="55" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="56" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="28" t="inlineStr">
@@ -2656,11 +2879,11 @@
           <t>Any operator performing revenue service on a route not appearing in this sheet requires written extra-service authorization from the Operations Duty Officer under Rule Book §4.12. No such authorization was issued for the 10/17/2025 → 10/18/2025 service night.</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="49" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="60" t="n"/>
+      <c r="E14" s="60" t="n"/>
+      <c r="F14" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2692,6 +2915,7 @@
           <t>ALDER CREEK TRANSIT DISTRICT — SCHEDULE NOTES</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="22" t="inlineStr">

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -127,7 +127,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -179,8 +179,20 @@
         <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E8C6"/>
+        <bgColor rgb="00C6E8C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDF0DD"/>
+        <bgColor rgb="00DDF0DD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -515,11 +527,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B8862B"/>
+      </left>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,6 +718,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1009,7 +1060,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — OPERATIONS</t>
         </is>
@@ -1157,7 +1208,7 @@
       <c r="N8" s="56" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Block Assignment Header</t>
         </is>
@@ -1182,7 +1233,7 @@
           <t>Block ID:</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>512-OWL</t>
         </is>
@@ -1214,7 +1265,7 @@
           <t>Operator Badge:</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>4417</t>
         </is>
@@ -1246,7 +1297,7 @@
           <t>Vehicle #:</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>4177</t>
         </is>
@@ -1278,7 +1329,7 @@
           <t>Scheduled Pullout:</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>10/17/2025 22:15</t>
         </is>
@@ -1310,7 +1361,7 @@
           <t>Sign / Bid Cycle:</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Fall 2025 Sign</t>
         </is>
@@ -1337,7 +1388,7 @@
       <c r="N15" s="56" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Block Manifest — Trip Roster</t>
         </is>
@@ -2293,7 +2344,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
         </is>
@@ -2377,7 +2428,7 @@
       <c r="N35" s="56" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Assignment Sign-Off</t>
         </is>
@@ -2618,7 +2669,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — AUTHORIZED OWL ROUTES</t>
         </is>
@@ -2707,7 +2758,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="65" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2739,7 +2790,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2771,7 +2822,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="65" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2803,7 +2854,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2835,7 +2886,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="65" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2867,7 +2918,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F12" s="47" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2910,7 +2961,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — SCHEDULE NOTES</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:05 (SB timepoint pass) / 02:31</t>
+          <t>02:05 (early control-point pass) / 02:31</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="63" t="inlineStr">
         <is>
-          <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
+          <t>Assignment Sign-Off</t>
         </is>
       </c>
       <c r="B32" s="54" t="n"/>
@@ -2366,54 +2366,62 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>Trip #</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Scheduled Timepoint</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C33" s="58" t="n"/>
+      <c r="D33" s="58" t="n"/>
+      <c r="E33" s="58" t="n"/>
+      <c r="F33" s="58" t="n"/>
+      <c r="G33" s="58" t="n"/>
+      <c r="H33" s="58" t="n"/>
+      <c r="I33" s="58" t="n"/>
+      <c r="J33" s="58" t="n"/>
+      <c r="K33" s="58" t="n"/>
+      <c r="L33" s="58" t="n"/>
+      <c r="M33" s="58" t="n"/>
+      <c r="N33" s="59" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>06 (SB pass, mid-loop reference)</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Southbound reference pass at S. Main / Third</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>10/18/2025 02:05</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Northbound leg 06 passes S. Main / Third at 02:31 following downtown loop; SB reference timepoint at 02:05 is the published control point for the trip pair 05/06 turnaround</t>
-        </is>
-      </c>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Operator (Badge / Name)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>4417 / Keeler, Raymond T.</t>
+        </is>
+      </c>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="55" t="n"/>
+      <c r="H34" s="55" t="n"/>
+      <c r="I34" s="55" t="n"/>
+      <c r="J34" s="55" t="n"/>
+      <c r="K34" s="55" t="n"/>
+      <c r="L34" s="55" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="56" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
-        </is>
-      </c>
-      <c r="B35" s="55" t="n"/>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Runcutter</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>J. Amaya, Sched. Analyst II</t>
+        </is>
+      </c>
       <c r="C35" s="55" t="n"/>
       <c r="D35" s="55" t="n"/>
       <c r="E35" s="55" t="n"/>
@@ -2427,59 +2435,87 @@
       <c r="M35" s="55" t="n"/>
       <c r="N35" s="56" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>R. Delcourt, Manager of Scheduling</t>
+        </is>
+      </c>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="55" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="55" t="n"/>
+      <c r="H36" s="55" t="n"/>
+      <c r="I36" s="55" t="n"/>
+      <c r="J36" s="55" t="n"/>
+      <c r="K36" s="55" t="n"/>
+      <c r="L36" s="55" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="56" t="n"/>
+    </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="63" t="inlineStr">
-        <is>
-          <t>Assignment Sign-Off</t>
-        </is>
-      </c>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="54" t="n"/>
-      <c r="G37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="54" t="n"/>
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Approval date</t>
+        </is>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>09/02/2025</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="55" t="n"/>
+      <c r="H37" s="55" t="n"/>
+      <c r="I37" s="55" t="n"/>
+      <c r="J37" s="55" t="n"/>
+      <c r="K37" s="55" t="n"/>
+      <c r="L37" s="55" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="56" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B38" s="57" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C38" s="58" t="n"/>
-      <c r="D38" s="58" t="n"/>
-      <c r="E38" s="58" t="n"/>
-      <c r="F38" s="58" t="n"/>
-      <c r="G38" s="58" t="n"/>
-      <c r="H38" s="58" t="n"/>
-      <c r="I38" s="58" t="n"/>
-      <c r="J38" s="58" t="n"/>
-      <c r="K38" s="58" t="n"/>
-      <c r="L38" s="58" t="n"/>
-      <c r="M38" s="58" t="n"/>
-      <c r="N38" s="59" t="n"/>
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Board of record</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>Rivergate Yard (Div. 3) — Owl Board</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="55" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="55" t="n"/>
+      <c r="H38" s="55" t="n"/>
+      <c r="I38" s="55" t="n"/>
+      <c r="J38" s="55" t="n"/>
+      <c r="K38" s="55" t="n"/>
+      <c r="L38" s="55" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="56" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Operator (Badge / Name)</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>4417 / Keeler, Raymond T.</t>
+          <t>Bid award reference</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Fall 2025 Sign — Owl Sr. Board Line 12</t>
         </is>
       </c>
       <c r="C39" s="55" t="n"/>
@@ -2495,126 +2531,11 @@
       <c r="M39" s="55" t="n"/>
       <c r="N39" s="56" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Runcutter</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>J. Amaya, Sched. Analyst II</t>
-        </is>
-      </c>
-      <c r="C40" s="55" t="n"/>
-      <c r="D40" s="55" t="n"/>
-      <c r="E40" s="55" t="n"/>
-      <c r="F40" s="55" t="n"/>
-      <c r="G40" s="55" t="n"/>
-      <c r="H40" s="55" t="n"/>
-      <c r="I40" s="55" t="n"/>
-      <c r="J40" s="55" t="n"/>
-      <c r="K40" s="55" t="n"/>
-      <c r="L40" s="55" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="56" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Approved by</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>R. Delcourt, Manager of Scheduling</t>
-        </is>
-      </c>
-      <c r="C41" s="55" t="n"/>
-      <c r="D41" s="55" t="n"/>
-      <c r="E41" s="55" t="n"/>
-      <c r="F41" s="55" t="n"/>
-      <c r="G41" s="55" t="n"/>
-      <c r="H41" s="55" t="n"/>
-      <c r="I41" s="55" t="n"/>
-      <c r="J41" s="55" t="n"/>
-      <c r="K41" s="55" t="n"/>
-      <c r="L41" s="55" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="56" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Approval date</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>09/02/2025</t>
-        </is>
-      </c>
-      <c r="C42" s="55" t="n"/>
-      <c r="D42" s="55" t="n"/>
-      <c r="E42" s="55" t="n"/>
-      <c r="F42" s="55" t="n"/>
-      <c r="G42" s="55" t="n"/>
-      <c r="H42" s="55" t="n"/>
-      <c r="I42" s="55" t="n"/>
-      <c r="J42" s="55" t="n"/>
-      <c r="K42" s="55" t="n"/>
-      <c r="L42" s="55" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="56" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>Board of record</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>Rivergate Yard (Div. 3) — Owl Board</t>
-        </is>
-      </c>
-      <c r="C43" s="55" t="n"/>
-      <c r="D43" s="55" t="n"/>
-      <c r="E43" s="55" t="n"/>
-      <c r="F43" s="55" t="n"/>
-      <c r="G43" s="55" t="n"/>
-      <c r="H43" s="55" t="n"/>
-      <c r="I43" s="55" t="n"/>
-      <c r="J43" s="55" t="n"/>
-      <c r="K43" s="55" t="n"/>
-      <c r="L43" s="55" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="56" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>Bid award reference</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>Fall 2025 Sign — Owl Sr. Board Line 12</t>
-        </is>
-      </c>
-      <c r="C44" s="55" t="n"/>
-      <c r="D44" s="55" t="n"/>
-      <c r="E44" s="55" t="n"/>
-      <c r="F44" s="55" t="n"/>
-      <c r="G44" s="55" t="n"/>
-      <c r="H44" s="55" t="n"/>
-      <c r="I44" s="55" t="n"/>
-      <c r="J44" s="55" t="n"/>
-      <c r="K44" s="55" t="n"/>
-      <c r="L44" s="55" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="56" t="n"/>
-    </row>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="G12:N12"/>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -180,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -515,11 +515,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B8862B"/>
+      </left>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,6 +706,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1009,7 +1048,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — OPERATIONS</t>
         </is>
@@ -1157,7 +1196,7 @@
       <c r="N8" s="56" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Block Assignment Header</t>
         </is>
@@ -1182,7 +1221,7 @@
           <t>Block ID:</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>512-OWL</t>
         </is>
@@ -1214,7 +1253,7 @@
           <t>Operator Badge:</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>4417</t>
         </is>
@@ -1246,7 +1285,7 @@
           <t>Vehicle #:</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>4177</t>
         </is>
@@ -1278,7 +1317,7 @@
           <t>Scheduled Pullout:</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>10/17/2025 22:15</t>
         </is>
@@ -1310,7 +1349,7 @@
           <t>Sign / Bid Cycle:</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Fall 2025 Sign</t>
         </is>
@@ -1337,7 +1376,7 @@
       <c r="N15" s="56" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Block Manifest — Trip Roster</t>
         </is>
@@ -1908,7 +1947,7 @@
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:05 (SB timepoint pass) / 02:31</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
@@ -2292,92 +2331,27 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
-        </is>
-      </c>
-      <c r="B32" s="54" t="n"/>
-      <c r="C32" s="54" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="54" t="n"/>
-      <c r="F32" s="54" t="n"/>
-      <c r="G32" s="54" t="n"/>
-      <c r="H32" s="54" t="n"/>
-      <c r="I32" s="54" t="n"/>
-      <c r="J32" s="54" t="n"/>
-      <c r="K32" s="54" t="n"/>
-      <c r="L32" s="54" t="n"/>
-      <c r="M32" s="54" t="n"/>
-      <c r="N32" s="54" t="n"/>
+      <c r="A32" s="65" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Trip #</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Scheduled Timepoint</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A33" s="66" t="n"/>
+      <c r="B33" s="66" t="n"/>
+      <c r="C33" s="66" t="n"/>
+      <c r="D33" s="66" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>06 (SB pass, mid-loop reference)</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Southbound reference pass at S. Main / Third</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>10/18/2025 02:05</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Northbound leg 06 passes S. Main / Third at 02:31 following downtown loop; SB reference timepoint at 02:05 is the published control point for the trip pair 05/06 turnaround</t>
-        </is>
-      </c>
+      <c r="A34" s="66" t="n"/>
+      <c r="B34" s="65" t="n"/>
+      <c r="C34" s="65" t="n"/>
+      <c r="D34" s="65" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
-        </is>
-      </c>
-      <c r="B35" s="55" t="n"/>
-      <c r="C35" s="55" t="n"/>
-      <c r="D35" s="55" t="n"/>
-      <c r="E35" s="55" t="n"/>
-      <c r="F35" s="55" t="n"/>
-      <c r="G35" s="55" t="n"/>
-      <c r="H35" s="55" t="n"/>
-      <c r="I35" s="55" t="n"/>
-      <c r="J35" s="55" t="n"/>
-      <c r="K35" s="55" t="n"/>
-      <c r="L35" s="55" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="56" t="n"/>
+      <c r="A35" s="65" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Assignment Sign-Off</t>
         </is>
@@ -2565,7 +2539,7 @@
       <c r="N44" s="56" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="27">
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G11:N11"/>
     <mergeCell ref="B40:N40"/>
@@ -2585,11 +2559,9 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="G14:N14"/>
     <mergeCell ref="B39:N39"/>
-    <mergeCell ref="A32:N32"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B42:N42"/>
     <mergeCell ref="A17:N17"/>
-    <mergeCell ref="A35:N35"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B44:N44"/>
@@ -2618,7 +2590,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — AUTHORIZED OWL ROUTES</t>
         </is>
@@ -2910,7 +2882,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — SCHEDULE NOTES</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -2331,7 +2331,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="65" t="n"/>
     </row>
@@ -2965,7 +2964,7 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>Bus #4177 was checked out to Block 512-OWL at Div. 3 on 10/17/2025 for the pullout at 22:15. Vehicle-to-block assignment reconciles to the Div. 3 pre-trip yard sheet and the fleet dispatch log.</t>
+          <t>Bus #4177 was checked out to Block 512-OWL at Div. 3 on 10/17/2025 for the pullout at 22:15. Vehicle-to-block assignment reconciles to the fleet dispatch log (pre-trip completion entry).</t>
         </is>
       </c>
     </row>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,12 @@
       <color rgb="002E6B3B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="008A5A00"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -543,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -719,6 +725,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2653,7 +2665,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>510</t>
         </is>
@@ -2685,7 +2697,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>511</t>
         </is>
@@ -2717,7 +2729,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>512</t>
         </is>
@@ -2749,7 +2761,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>514</t>
         </is>
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>517</t>
         </is>
@@ -2813,7 +2825,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>519</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,8 +132,14 @@
       <color rgb="008A5A00"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="FF1E5631"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +191,12 @@
         <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAD7"/>
+        <bgColor rgb="FFD6EAD7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -549,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,6 +743,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2690,7 +2705,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2722,7 +2737,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2754,7 +2769,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2786,7 +2801,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2818,7 +2833,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
@@ -2850,7 +2865,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F12" s="47" t="inlineStr">
+      <c r="F12" s="69" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -1614,22 +1614,22 @@
       </c>
       <c r="J20" s="33" t="inlineStr">
         <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="L20" s="33" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="M20" s="33" t="inlineStr">
+        <is>
           <t>22:51</t>
-        </is>
-      </c>
-      <c r="K20" s="33" t="inlineStr">
-        <is>
-          <t>22:58</t>
-        </is>
-      </c>
-      <c r="L20" s="33" t="inlineStr">
-        <is>
-          <t>23:07</t>
-        </is>
-      </c>
-      <c r="M20" s="33" t="inlineStr">
-        <is>
-          <t>23:19</t>
         </is>
       </c>
       <c r="N20" s="34" t="inlineStr">
@@ -1681,22 +1681,22 @@
       </c>
       <c r="I21" s="30" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="J21" s="30" t="inlineStr">
         <is>
-          <t>23:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="K21" s="30" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="L21" s="30" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="M21" s="30" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="N21" s="31" t="inlineStr">
         <is>
-          <t>Layover 23:19–23:24 at Rivergate Plaza</t>
+          <t>Layover 22:51–23:24 at Rivergate Plaza</t>
         </is>
       </c>
     </row>
@@ -1758,27 +1758,27 @@
       </c>
       <c r="J22" s="33" t="inlineStr">
         <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="K22" s="33" t="inlineStr">
+        <is>
+          <t>00:07</t>
+        </is>
+      </c>
+      <c r="L22" s="33" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="M22" s="33" t="inlineStr">
+        <is>
           <t>00:11</t>
         </is>
       </c>
-      <c r="K22" s="33" t="inlineStr">
-        <is>
-          <t>00:18</t>
-        </is>
-      </c>
-      <c r="L22" s="33" t="inlineStr">
-        <is>
-          <t>00:27</t>
-        </is>
-      </c>
-      <c r="M22" s="33" t="inlineStr">
-        <is>
-          <t>00:39</t>
-        </is>
-      </c>
       <c r="N22" s="34" t="inlineStr">
         <is>
-          <t>Layover 23:57–00:05 at S. Main/Fifth</t>
+          <t>Layover 23:30–00:05 at S. Main/Fifth</t>
         </is>
       </c>
     </row>
@@ -1825,22 +1825,22 @@
       </c>
       <c r="I23" s="30" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>00:50</t>
         </is>
       </c>
       <c r="J23" s="30" t="inlineStr">
         <is>
-          <t>01:11</t>
+          <t>00:49</t>
         </is>
       </c>
       <c r="K23" s="30" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>00:48</t>
         </is>
       </c>
       <c r="L23" s="30" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="M23" s="30" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N23" s="31" t="inlineStr">
         <is>
-          <t>Layover 00:39–00:44 at Rivergate Plaza</t>
+          <t>Layover 00:11–00:44 at Rivergate Plaza</t>
         </is>
       </c>
     </row>
@@ -1902,27 +1902,27 @@
       </c>
       <c r="J24" s="33" t="inlineStr">
         <is>
+          <t>01:26</t>
+        </is>
+      </c>
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="L24" s="33" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="M24" s="33" t="inlineStr">
+        <is>
           <t>01:31</t>
         </is>
       </c>
-      <c r="K24" s="33" t="inlineStr">
-        <is>
-          <t>01:38</t>
-        </is>
-      </c>
-      <c r="L24" s="33" t="inlineStr">
-        <is>
-          <t>01:47</t>
-        </is>
-      </c>
-      <c r="M24" s="33" t="inlineStr">
-        <is>
-          <t>01:59</t>
-        </is>
-      </c>
       <c r="N24" s="34" t="inlineStr">
         <is>
-          <t>Layover 01:17–01:25 at S. Main/Fifth</t>
+          <t>Layover 00:50–01:25 at S. Main/Fifth</t>
         </is>
       </c>
     </row>
@@ -1969,22 +1969,22 @@
       </c>
       <c r="I25" s="30" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:31</t>
+          <t>02:09</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
         <is>
-          <t>02:24</t>
+          <t>02:08</t>
         </is>
       </c>
       <c r="L25" s="30" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>02:06</t>
         </is>
       </c>
       <c r="M25" s="30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="N25" s="31" t="inlineStr">
         <is>
-          <t>Layover 01:59–02:04 at Rivergate Plaza</t>
+          <t>Layover 01:31–02:04 at Rivergate Plaza</t>
         </is>
       </c>
     </row>
@@ -2046,27 +2046,27 @@
       </c>
       <c r="J26" s="33" t="inlineStr">
         <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="K26" s="33" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="L26" s="33" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="M26" s="33" t="inlineStr">
+        <is>
           <t>02:51</t>
         </is>
       </c>
-      <c r="K26" s="33" t="inlineStr">
-        <is>
-          <t>02:58</t>
-        </is>
-      </c>
-      <c r="L26" s="33" t="inlineStr">
-        <is>
-          <t>03:07</t>
-        </is>
-      </c>
-      <c r="M26" s="33" t="inlineStr">
-        <is>
-          <t>03:19</t>
-        </is>
-      </c>
       <c r="N26" s="34" t="inlineStr">
         <is>
-          <t>Layover 02:37–02:45 at S. Main/Fifth</t>
+          <t>Layover 02:10–02:45 at S. Main/Fifth</t>
         </is>
       </c>
     </row>
@@ -2113,22 +2113,22 @@
       </c>
       <c r="I27" s="30" t="inlineStr">
         <is>
-          <t>03:57</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="J27" s="30" t="inlineStr">
         <is>
-          <t>03:51</t>
+          <t>03:29</t>
         </is>
       </c>
       <c r="K27" s="30" t="inlineStr">
         <is>
-          <t>03:44</t>
+          <t>03:28</t>
         </is>
       </c>
       <c r="L27" s="30" t="inlineStr">
         <is>
-          <t>03:35</t>
+          <t>03:26</t>
         </is>
       </c>
       <c r="M27" s="30" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="N27" s="31" t="inlineStr">
         <is>
-          <t>Layover 03:19–03:24 at Rivergate Plaza</t>
+          <t>Layover 02:51–03:24 at Rivergate Plaza</t>
         </is>
       </c>
     </row>
@@ -2190,27 +2190,27 @@
       </c>
       <c r="J28" s="33" t="inlineStr">
         <is>
+          <t>04:06</t>
+        </is>
+      </c>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="L28" s="33" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="inlineStr">
+        <is>
           <t>04:11</t>
         </is>
       </c>
-      <c r="K28" s="33" t="inlineStr">
-        <is>
-          <t>04:18</t>
-        </is>
-      </c>
-      <c r="L28" s="33" t="inlineStr">
-        <is>
-          <t>04:27</t>
-        </is>
-      </c>
-      <c r="M28" s="33" t="inlineStr">
-        <is>
-          <t>04:39</t>
-        </is>
-      </c>
       <c r="N28" s="34" t="inlineStr">
         <is>
-          <t>Layover 03:57–04:05 at S. Main/Fifth</t>
+          <t>Layover 03:30–04:05 at S. Main/Fifth</t>
         </is>
       </c>
     </row>
@@ -2257,17 +2257,17 @@
       </c>
       <c r="I29" s="30" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="J29" s="30" t="inlineStr">
         <is>
-          <t>04:54</t>
+          <t>04:49</t>
         </is>
       </c>
       <c r="K29" s="30" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="L29" s="30" t="inlineStr">

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -180,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -515,11 +515,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C2B3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C2B3"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B8862B"/>
+      </left>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00B8862B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,6 +706,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1009,7 +1042,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — OPERATIONS</t>
         </is>
@@ -1157,7 +1190,7 @@
       <c r="N8" s="56" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Block Assignment Header</t>
         </is>
@@ -1182,7 +1215,7 @@
           <t>Block ID:</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>512-OWL</t>
         </is>
@@ -1214,7 +1247,7 @@
           <t>Operator Badge:</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>4417</t>
         </is>
@@ -1246,7 +1279,7 @@
           <t>Vehicle #:</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>4177</t>
         </is>
@@ -1278,7 +1311,7 @@
           <t>Scheduled Pullout:</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>10/17/2025 22:15</t>
         </is>
@@ -1310,7 +1343,7 @@
           <t>Sign / Bid Cycle:</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Fall 2025 Sign</t>
         </is>
@@ -1337,7 +1370,7 @@
       <c r="N15" s="56" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Block Manifest — Trip Roster</t>
         </is>
@@ -2293,7 +2326,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
         </is>
@@ -2377,7 +2410,7 @@
       <c r="N35" s="56" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Assignment Sign-Off</t>
         </is>
@@ -2618,7 +2651,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — AUTHORIZED OWL ROUTES</t>
         </is>
@@ -2910,7 +2943,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>ALDER CREEK TRANSIT DISTRICT — SCHEDULE NOTES</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J25" s="30" t="inlineStr">
         <is>
-          <t>02:05 (SB timepoint pass) / 02:31</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="K25" s="30" t="inlineStr">
@@ -2370,29 +2370,29 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>06 (SB pass, mid-loop reference)</t>
+          <t>06 (NB, primary reference)</t>
         </is>
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>Southbound reference pass at S. Main / Third</t>
+          <t>Northbound revenue pass at S. Main / Third</t>
         </is>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>10/18/2025 02:05</t>
+          <t>10/18/2025 02:31</t>
         </is>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>Northbound leg 06 passes S. Main / Third at 02:31 following downtown loop; SB reference timepoint at 02:05 is the published control point for the trip pair 05/06 turnaround</t>
+          <t>Trip 06 departs Poplar / Rivergate Plaza at 02:04 and passes S. Main / Third northbound at 02:31 following the downtown loop; this is the published control point for the trip pair 05/06 turnaround</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>Timepoint reference: the 02:05 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
+          <t>Timepoint reference: the 02:31 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
         </is>
       </c>
       <c r="B35" s="55" t="n"/>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,8 +126,14 @@
       <color rgb="002E6B3B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="008A6420"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -179,6 +185,12 @@
         <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -543,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -714,6 +726,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2715,7 +2736,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>510</t>
         </is>
@@ -2740,14 +2761,14 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>511</t>
         </is>
@@ -2772,14 +2793,14 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>512</t>
         </is>
@@ -2804,14 +2825,14 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>514</t>
         </is>
@@ -2836,14 +2857,14 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>517</t>
         </is>
@@ -2868,14 +2889,14 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>519</t>
         </is>
@@ -2900,7 +2921,7 @@
           <t>60 min</t>
         </is>
       </c>
-      <c r="F12" s="47" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>

--- a/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
+++ b/filesystem/ACTD/Ops/RunSchedule_Owl512.xlsx
@@ -1043,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2349,7 +2349,7 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="63" t="inlineStr">
         <is>
-          <t>Key Timepoint — S. Main / Third (Downtown Rivergate)</t>
+          <t>Assignment Sign-Off</t>
         </is>
       </c>
       <c r="B32" s="54" t="n"/>
@@ -2369,54 +2369,62 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>Trip #</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Scheduled Timepoint</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C33" s="58" t="n"/>
+      <c r="D33" s="58" t="n"/>
+      <c r="E33" s="58" t="n"/>
+      <c r="F33" s="58" t="n"/>
+      <c r="G33" s="58" t="n"/>
+      <c r="H33" s="58" t="n"/>
+      <c r="I33" s="58" t="n"/>
+      <c r="J33" s="58" t="n"/>
+      <c r="K33" s="58" t="n"/>
+      <c r="L33" s="58" t="n"/>
+      <c r="M33" s="58" t="n"/>
+      <c r="N33" s="59" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>06 (NB, primary reference)</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Northbound revenue pass at S. Main / Third</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>10/18/2025 02:31</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Trip 06 departs Poplar / Rivergate Plaza at 02:04 and passes S. Main / Third northbound at 02:31 following the downtown loop; this is the published control point for the trip pair 05/06 turnaround</t>
-        </is>
-      </c>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Operator (Badge / Name)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>4417 / Keeler, Raymond T.</t>
+        </is>
+      </c>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="55" t="n"/>
+      <c r="H34" s="55" t="n"/>
+      <c r="I34" s="55" t="n"/>
+      <c r="J34" s="55" t="n"/>
+      <c r="K34" s="55" t="n"/>
+      <c r="L34" s="55" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="56" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>Timepoint reference: the 02:31 a.m. control point at S. Main / Third is a published headway anchor for Trip pair 05/06 and is used by dispatch for on-time performance measurement.</t>
-        </is>
-      </c>
-      <c r="B35" s="55" t="n"/>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Runcutter</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>J. Amaya, Sched. Analyst II</t>
+        </is>
+      </c>
       <c r="C35" s="55" t="n"/>
       <c r="D35" s="55" t="n"/>
       <c r="E35" s="55" t="n"/>
@@ -2430,59 +2438,87 @@
       <c r="M35" s="55" t="n"/>
       <c r="N35" s="56" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>R. Delcourt, Manager of Scheduling</t>
+        </is>
+      </c>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="55" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="55" t="n"/>
+      <c r="H36" s="55" t="n"/>
+      <c r="I36" s="55" t="n"/>
+      <c r="J36" s="55" t="n"/>
+      <c r="K36" s="55" t="n"/>
+      <c r="L36" s="55" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="56" t="n"/>
+    </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="63" t="inlineStr">
-        <is>
-          <t>Assignment Sign-Off</t>
-        </is>
-      </c>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="54" t="n"/>
-      <c r="G37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="54" t="n"/>
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Approval date</t>
+        </is>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>09/02/2025</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="55" t="n"/>
+      <c r="H37" s="55" t="n"/>
+      <c r="I37" s="55" t="n"/>
+      <c r="J37" s="55" t="n"/>
+      <c r="K37" s="55" t="n"/>
+      <c r="L37" s="55" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="56" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B38" s="57" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C38" s="58" t="n"/>
-      <c r="D38" s="58" t="n"/>
-      <c r="E38" s="58" t="n"/>
-      <c r="F38" s="58" t="n"/>
-      <c r="G38" s="58" t="n"/>
-      <c r="H38" s="58" t="n"/>
-      <c r="I38" s="58" t="n"/>
-      <c r="J38" s="58" t="n"/>
-      <c r="K38" s="58" t="n"/>
-      <c r="L38" s="58" t="n"/>
-      <c r="M38" s="58" t="n"/>
-      <c r="N38" s="59" t="n"/>
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Board of record</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>Rivergate Yard (Div. 3) — Owl Board</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="55" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="55" t="n"/>
+      <c r="H38" s="55" t="n"/>
+      <c r="I38" s="55" t="n"/>
+      <c r="J38" s="55" t="n"/>
+      <c r="K38" s="55" t="n"/>
+      <c r="L38" s="55" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="56" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Operator (Badge / Name)</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>4417 / Keeler, Raymond T.</t>
+          <t>Bid award reference</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Fall 2025 Sign — Owl Sr. Board Line 12</t>
         </is>
       </c>
       <c r="C39" s="55" t="n"/>
@@ -2498,157 +2534,40 @@
       <c r="M39" s="55" t="n"/>
       <c r="N39" s="56" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Runcutter</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>J. Amaya, Sched. Analyst II</t>
-        </is>
-      </c>
-      <c r="C40" s="55" t="n"/>
-      <c r="D40" s="55" t="n"/>
-      <c r="E40" s="55" t="n"/>
-      <c r="F40" s="55" t="n"/>
-      <c r="G40" s="55" t="n"/>
-      <c r="H40" s="55" t="n"/>
-      <c r="I40" s="55" t="n"/>
-      <c r="J40" s="55" t="n"/>
-      <c r="K40" s="55" t="n"/>
-      <c r="L40" s="55" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="56" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Approved by</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>R. Delcourt, Manager of Scheduling</t>
-        </is>
-      </c>
-      <c r="C41" s="55" t="n"/>
-      <c r="D41" s="55" t="n"/>
-      <c r="E41" s="55" t="n"/>
-      <c r="F41" s="55" t="n"/>
-      <c r="G41" s="55" t="n"/>
-      <c r="H41" s="55" t="n"/>
-      <c r="I41" s="55" t="n"/>
-      <c r="J41" s="55" t="n"/>
-      <c r="K41" s="55" t="n"/>
-      <c r="L41" s="55" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="56" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Approval date</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>09/02/2025</t>
-        </is>
-      </c>
-      <c r="C42" s="55" t="n"/>
-      <c r="D42" s="55" t="n"/>
-      <c r="E42" s="55" t="n"/>
-      <c r="F42" s="55" t="n"/>
-      <c r="G42" s="55" t="n"/>
-      <c r="H42" s="55" t="n"/>
-      <c r="I42" s="55" t="n"/>
-      <c r="J42" s="55" t="n"/>
-      <c r="K42" s="55" t="n"/>
-      <c r="L42" s="55" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="56" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>Board of record</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>Rivergate Yard (Div. 3) — Owl Board</t>
-        </is>
-      </c>
-      <c r="C43" s="55" t="n"/>
-      <c r="D43" s="55" t="n"/>
-      <c r="E43" s="55" t="n"/>
-      <c r="F43" s="55" t="n"/>
-      <c r="G43" s="55" t="n"/>
-      <c r="H43" s="55" t="n"/>
-      <c r="I43" s="55" t="n"/>
-      <c r="J43" s="55" t="n"/>
-      <c r="K43" s="55" t="n"/>
-      <c r="L43" s="55" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="56" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>Bid award reference</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>Fall 2025 Sign — Owl Sr. Board Line 12</t>
-        </is>
-      </c>
-      <c r="C44" s="55" t="n"/>
-      <c r="D44" s="55" t="n"/>
-      <c r="E44" s="55" t="n"/>
-      <c r="F44" s="55" t="n"/>
-      <c r="G44" s="55" t="n"/>
-      <c r="H44" s="55" t="n"/>
-      <c r="I44" s="55" t="n"/>
-      <c r="J44" s="55" t="n"/>
-      <c r="K44" s="55" t="n"/>
-      <c r="L44" s="55" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="56" t="n"/>
-    </row>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="27">
+    <mergeCell ref="B37:N37"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G11:N11"/>
-    <mergeCell ref="B40:N40"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B33:N33"/>
     <mergeCell ref="B6:N6"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B5:N5"/>
-    <mergeCell ref="B41:N41"/>
+    <mergeCell ref="B36:N36"/>
+    <mergeCell ref="B35:N35"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="G13:N13"/>
-    <mergeCell ref="A37:N37"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="G15:N15"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B43:N43"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="G14:N14"/>
     <mergeCell ref="B39:N39"/>
     <mergeCell ref="A32:N32"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B42:N42"/>
     <mergeCell ref="A17:N17"/>
-    <mergeCell ref="A35:N35"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B44:N44"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="B38:N38"/>
+    <mergeCell ref="B34:N34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
